--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D3">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E3">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="G3">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <v>426</v>
